--- a/AircraftDesignToolbox-Feb23/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_TestCases.xlsx
+++ b/AircraftDesignToolbox-Feb23/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_TestCases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu-my.sharepoint.com/personal/aska7164_colorado_edu/Documents/Desktop/AircraftDesignToolbox-Feb23/MAIN/Input Excel Sheets/Design Configurations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\Files\College\Boulder\Senior\Fall\Design\Code\Senior-Project-Team-NMNAL\AircraftDesignToolbox-Feb23\MAIN\Input Excel Sheets\Design Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{AF967D3A-6581-5D40-BFFA-E1DDAEB3102C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{629D4DBD-6883-4C2C-B6FC-93FEE0294A4C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB35F6D8-7E62-4561-8670-EC1E72DF2058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" activeTab="5" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="251">
   <si>
     <t>Length_f</t>
   </si>
@@ -1107,6 +1107,12 @@
   </si>
   <si>
     <t>Electric -&gt; jet = 0</t>
+  </si>
+  <si>
+    <t>Push/Pull</t>
+  </si>
+  <si>
+    <t>NACA4412</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1536,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId3"/>
-      <xxl21:relativeUrl r:id="rId4"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Variable Reference"/>
@@ -2053,12 +2058,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6DAC46-A25C-47BF-94AD-A8C1FE6816F1}">
   <dimension ref="A1:D82"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="104.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="104.46484375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2104,7 +2109,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.8">
+    <row r="4" spans="1:4" ht="28.5">
       <c r="A4" s="3" t="s">
         <v>163</v>
       </c>
@@ -2118,7 +2123,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28.8">
+    <row r="5" spans="1:4" ht="28.5">
       <c r="A5" s="3" t="s">
         <v>163</v>
       </c>
@@ -2202,7 +2207,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.8">
+    <row r="11" spans="1:4" ht="28.5">
       <c r="A11" s="3" t="s">
         <v>163</v>
       </c>
@@ -2230,7 +2235,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.8">
+    <row r="13" spans="1:4" ht="28.5">
       <c r="A13" s="3" t="s">
         <v>163</v>
       </c>
@@ -2244,7 +2249,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="28.8">
+    <row r="14" spans="1:4" ht="28.5">
       <c r="A14" s="3" t="s">
         <v>163</v>
       </c>
@@ -2258,7 +2263,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.8">
+    <row r="15" spans="1:4" ht="28.5">
       <c r="A15" s="3" t="s">
         <v>163</v>
       </c>
@@ -2272,7 +2277,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28.8">
+    <row r="16" spans="1:4" ht="28.5">
       <c r="A16" s="3" t="s">
         <v>163</v>
       </c>
@@ -2342,7 +2347,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="43.2">
+    <row r="21" spans="1:4" ht="42.75">
       <c r="A21" s="3" t="s">
         <v>163</v>
       </c>
@@ -2370,7 +2375,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="28.8">
+    <row r="23" spans="1:4" ht="28.5">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2398,7 +2403,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="28.8">
+    <row r="25" spans="1:4" ht="28.5">
       <c r="A25" s="3" t="s">
         <v>163</v>
       </c>
@@ -2426,7 +2431,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="28.8">
+    <row r="27" spans="1:4" ht="28.5">
       <c r="A27" s="3" t="s">
         <v>163</v>
       </c>
@@ -2440,7 +2445,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="43.2">
+    <row r="28" spans="1:4" ht="42.75">
       <c r="A28" s="3" t="s">
         <v>163</v>
       </c>
@@ -2454,7 +2459,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="28.8">
+    <row r="29" spans="1:4" ht="28.5">
       <c r="A29" s="3" t="s">
         <v>163</v>
       </c>
@@ -2468,7 +2473,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="28.8">
+    <row r="30" spans="1:4" ht="28.5">
       <c r="A30" s="3" t="s">
         <v>163</v>
       </c>
@@ -2496,7 +2501,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="28.8">
+    <row r="32" spans="1:4" ht="28.5">
       <c r="A32" s="3" t="s">
         <v>163</v>
       </c>
@@ -2524,7 +2529,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="28.8">
+    <row r="34" spans="1:4" ht="28.5">
       <c r="A34" s="3" t="s">
         <v>163</v>
       </c>
@@ -2538,7 +2543,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="43.2">
+    <row r="35" spans="1:4" ht="42.75">
       <c r="A35" s="3" t="s">
         <v>163</v>
       </c>
@@ -2552,7 +2557,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="28.8">
+    <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
         <v>163</v>
       </c>
@@ -2566,7 +2571,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="28.8">
+    <row r="37" spans="1:4" ht="28.5">
       <c r="A37" s="3" t="s">
         <v>163</v>
       </c>
@@ -2594,7 +2599,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="28.8">
+    <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
         <v>163</v>
       </c>
@@ -2622,7 +2627,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="28.8">
+    <row r="41" spans="1:4" ht="28.5">
       <c r="A41" s="3" t="s">
         <v>163</v>
       </c>
@@ -2636,7 +2641,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="43.2">
+    <row r="42" spans="1:4" ht="42.75">
       <c r="A42" s="3" t="s">
         <v>163</v>
       </c>
@@ -2650,7 +2655,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="28.8">
+    <row r="43" spans="1:4">
       <c r="A43" s="3" t="s">
         <v>163</v>
       </c>
@@ -2664,7 +2669,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="28.8">
+    <row r="44" spans="1:4" ht="28.5">
       <c r="A44" s="3" t="s">
         <v>163</v>
       </c>
@@ -2692,7 +2697,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="28.8">
+    <row r="46" spans="1:4">
       <c r="A46" s="3" t="s">
         <v>163</v>
       </c>
@@ -2720,7 +2725,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="28.8">
+    <row r="48" spans="1:4" ht="28.5">
       <c r="A48" s="3" t="s">
         <v>163</v>
       </c>
@@ -2734,7 +2739,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="43.2">
+    <row r="49" spans="1:4" ht="42.75">
       <c r="A49" s="3" t="s">
         <v>163</v>
       </c>
@@ -3055,7 +3060,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="28.8">
+    <row r="73" spans="1:4" ht="28.5">
       <c r="A73" s="3" t="s">
         <v>191</v>
       </c>
@@ -3111,7 +3116,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="28.8">
+    <row r="77" spans="1:4" ht="28.5">
       <c r="A77" s="3" t="s">
         <v>191</v>
       </c>
@@ -3125,7 +3130,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="28.8">
+    <row r="78" spans="1:4" ht="28.5">
       <c r="A78" s="3" t="s">
         <v>191</v>
       </c>
@@ -3203,22 +3208,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ADD393-55AB-49FB-9382-D2896E9EB980}">
   <dimension ref="A1:AV21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="4"/>
+    <col min="1" max="1" width="8.796875" style="4"/>
     <col min="2" max="2" width="26.6640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" style="4" customWidth="1"/>
-    <col min="4" max="12" width="8.77734375" style="4"/>
-    <col min="13" max="13" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.77734375" style="4"/>
+    <col min="3" max="3" width="9.796875" style="4" customWidth="1"/>
+    <col min="4" max="12" width="8.796875" style="4"/>
+    <col min="13" max="13" width="6.796875" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.796875" style="4"/>
     <col min="15" max="15" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.77734375" style="4"/>
-    <col min="17" max="17" width="10.44140625" style="4" customWidth="1"/>
-    <col min="18" max="18" width="16.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="35" width="8.77734375" style="4"/>
+    <col min="16" max="16" width="8.796875" style="4"/>
+    <col min="17" max="17" width="10.46484375" style="4" customWidth="1"/>
+    <col min="18" max="18" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="35" width="8.796875" style="4"/>
     <col min="36" max="36" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="8.77734375" style="4"/>
+    <col min="37" max="16384" width="8.796875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48">
@@ -4257,6 +4262,170 @@
       </c>
       <c r="AV7" s="4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48">
+      <c r="A8" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="4">
+        <v>8000</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="F8" s="4">
+        <f>44/12</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G8" s="4">
+        <f>7/12</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H8" s="4">
+        <f>F8/G8</f>
+        <v>6.2857142857142847</v>
+      </c>
+      <c r="I8" s="4">
+        <f>(PI()/4)*G8^2</f>
+        <v>0.26725354171163174</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <f>F8*PI()*G8</f>
+        <v>6.719517620178169</v>
+      </c>
+      <c r="L8" s="4">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="N8" s="4">
+        <v>4</v>
+      </c>
+      <c r="O8" s="4">
+        <f>2*N8</f>
+        <v>8</v>
+      </c>
+      <c r="P8" s="4">
+        <f>(4^2)/N8</f>
+        <v>4</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>1</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U8" s="4">
+        <v>2</v>
+      </c>
+      <c r="V8" s="4">
+        <f>2*U8</f>
+        <v>4</v>
+      </c>
+      <c r="W8" s="4">
+        <v>2</v>
+      </c>
+      <c r="X8" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <v>0.58330000000000004</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f>2*AI8</f>
+        <v>1.1666000000000001</v>
+      </c>
+      <c r="AK8" s="4">
+        <f>1/AI8</f>
+        <v>1.7143836790673752</v>
+      </c>
+      <c r="AL8" s="4">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AM8" s="4">
+        <f>ATAN(10/8)*180/PI()</f>
+        <v>51.340191745909912</v>
+      </c>
+      <c r="AN8" s="4">
+        <f>7/12</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="AO8" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP8" s="4">
+        <v>0.58330000000000004</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f>2*AP8</f>
+        <v>1.1666000000000001</v>
+      </c>
+      <c r="AR8" s="4">
+        <f>1/AP8</f>
+        <v>1.7143836790673752</v>
+      </c>
+      <c r="AS8" s="4">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AT8" s="4">
+        <f>ATAN(10/8)*180/PI()</f>
+        <v>51.340191745909912</v>
+      </c>
+      <c r="AU8" s="4">
+        <f>7/12</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="AV8" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="21" s="22" customFormat="1"/>
@@ -4280,21 +4449,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538960B4-04F0-4DA1-BF31-3569558CC234}">
   <dimension ref="A1:BB21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="10"/>
-    <col min="2" max="2" width="11.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="42" width="8.77734375" style="10"/>
-    <col min="43" max="43" width="11.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.77734375" style="10"/>
-    <col min="45" max="45" width="9.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="8.77734375" style="10"/>
+    <col min="1" max="1" width="8.796875" style="10"/>
+    <col min="2" max="2" width="11.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="42" width="8.796875" style="10"/>
+    <col min="43" max="43" width="11.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.796875" style="10"/>
+    <col min="45" max="45" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.796875" style="10"/>
     <col min="48" max="49" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.77734375" style="10"/>
+    <col min="50" max="50" width="8.796875" style="10"/>
     <col min="51" max="51" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="53" max="16384" width="8.77734375" style="10"/>
+    <col min="52" max="52" width="11.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="53" max="16384" width="8.796875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54">
@@ -5461,6 +5630,170 @@
       </c>
       <c r="BB7" s="10">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54">
+      <c r="A8" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="10">
+        <v>-0.43940000000000001</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-0.33539999999999998</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-0.2321</v>
+      </c>
+      <c r="H8" s="10">
+        <v>-0.14319999999999999</v>
+      </c>
+      <c r="I8" s="10">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0.1804</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0.31659999999999999</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0.4299</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0.52790000000000004</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0.70940000000000003</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0.77370000000000005</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="R8" s="10">
+        <v>0.90810000000000002</v>
+      </c>
+      <c r="S8" s="10">
+        <v>1.2725</v>
+      </c>
+      <c r="T8" s="10">
+        <v>1.3248</v>
+      </c>
+      <c r="U8" s="10">
+        <v>1.3527</v>
+      </c>
+      <c r="V8" s="10">
+        <v>1.4092</v>
+      </c>
+      <c r="W8" s="10">
+        <v>1.4298</v>
+      </c>
+      <c r="X8" s="10">
+        <v>7.85E-2</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>4.419E-2</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>3.6269999999999997E-2</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>3.3689999999999998E-2</v>
+      </c>
+      <c r="AB8" s="10">
+        <v>3.2579999999999998E-2</v>
+      </c>
+      <c r="AC8" s="10">
+        <v>3.3180000000000001E-2</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>3.6569999999999998E-2</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>4.0140000000000002E-2</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>4.4260000000000001E-2</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>4.8320000000000002E-2</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>5.3749999999999999E-2</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>6.012E-2</v>
+      </c>
+      <c r="AJ8" s="10">
+        <v>6.6339999999999996E-2</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>7.1929999999999994E-2</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>4.1549999999999997E-2</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>3.9910000000000001E-2</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>4.7419999999999997E-2</v>
+      </c>
+      <c r="AO8" s="10">
+        <v>5.7959999999999998E-2</v>
+      </c>
+      <c r="AP8" s="10">
+        <v>3.9419999999999997E-2</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="AR8" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="AS8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="AX8" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="AY8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ8" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="BA8" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="BB8" s="10">
+        <v>0.3</v>
       </c>
     </row>
     <row r="21" s="23" customFormat="1"/>
@@ -5473,13 +5806,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B77D4EB-A9CB-4E6A-B1A1-7AF90F186000}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.46484375" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5876,6 +6209,32 @@
         <v>0</v>
       </c>
       <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
@@ -5920,11 +6279,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5CDADA5-6988-44B9-AE9F-DADE8E93F984}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="26.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6055,7 +6414,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB49278-C885-4626-918F-22B9EA08CAD8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
